--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324393</v>
       </c>
       <c r="B2" t="n">
-        <v>98399</v>
+        <v>98402</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123324394</v>
       </c>
       <c r="B3" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324393</v>
       </c>
       <c r="B2" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123324394</v>
       </c>
       <c r="B3" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324393</v>
       </c>
       <c r="B2" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123324394</v>
       </c>
       <c r="B3" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324393</v>
+        <v>123324394</v>
       </c>
       <c r="B2" t="n">
-        <v>98410</v>
+        <v>98296</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599204</v>
+        <v>599230</v>
       </c>
       <c r="R2" t="n">
-        <v>6929083</v>
+        <v>6929200</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1223</t>
+          <t>2024_1222</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324394</v>
+        <v>123324393</v>
       </c>
       <c r="B3" t="n">
-        <v>98293</v>
+        <v>98413</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599230</v>
+        <v>599204</v>
       </c>
       <c r="R3" t="n">
-        <v>6929200</v>
+        <v>6929083</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1222</t>
+          <t>2024_1223</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324394</v>
+        <v>123324393</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599230</v>
+        <v>599204</v>
       </c>
       <c r="R2" t="n">
-        <v>6929200</v>
+        <v>6929083</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1222</t>
+          <t>2024_1223</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324393</v>
+        <v>123324394</v>
       </c>
       <c r="B3" t="n">
-        <v>98413</v>
+        <v>98313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599204</v>
+        <v>599230</v>
       </c>
       <c r="R3" t="n">
-        <v>6929083</v>
+        <v>6929200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1223</t>
+          <t>2024_1222</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324393</v>
+        <v>123324394</v>
       </c>
       <c r="B2" t="n">
-        <v>98430</v>
+        <v>98419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599204</v>
+        <v>599230</v>
       </c>
       <c r="R2" t="n">
-        <v>6929083</v>
+        <v>6929200</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1223</t>
+          <t>2024_1222</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324394</v>
+        <v>123324393</v>
       </c>
       <c r="B3" t="n">
-        <v>98313</v>
+        <v>98536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599230</v>
+        <v>599204</v>
       </c>
       <c r="R3" t="n">
-        <v>6929200</v>
+        <v>6929083</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1222</t>
+          <t>2024_1223</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324394</v>
       </c>
       <c r="B2" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123324393</v>
       </c>
       <c r="B3" t="n">
-        <v>98536</v>
+        <v>98538</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324394</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123324393</v>
       </c>
       <c r="B3" t="n">
-        <v>98538</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21609-2024 artfynd.xlsx
+++ b/artfynd/A 21609-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324394</v>
+        <v>123324393</v>
       </c>
       <c r="B2" t="n">
-        <v>97996</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599230</v>
+        <v>599204</v>
       </c>
       <c r="R2" t="n">
-        <v>6929200</v>
+        <v>6929083</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1222</t>
+          <t>2024_1223</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324393</v>
+        <v>123324394</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>97996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599204</v>
+        <v>599230</v>
       </c>
       <c r="R3" t="n">
-        <v>6929083</v>
+        <v>6929200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1223</t>
+          <t>2024_1222</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
